--- a/site/assets/project_horizon_model.xlsx
+++ b/site/assets/project_horizon_model.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1040.9</v>
+        <v>1047.2</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>30557.259004693</v>
+        <v>30569.40578845</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>185926.1127487379</v>
+        <v>186000.0200414696</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>40841.39852378159</v>
+        <v>40857.63334497828</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>8919.067319154374</v>
+        <v>8922.612728185441</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>34182.07067543484</v>
+        <v>34195.6583542511</v>
       </c>
     </row>
     <row r="9">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>8551167.338222595</v>
+        <v>8554566.503720764</v>
       </c>
     </row>
     <row r="10">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4580.6</v>
+        <v>4682.7</v>
       </c>
     </row>
     <row r="12">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5405.11</v>
+        <v>5525.59</v>
       </c>
     </row>
     <row r="20">
@@ -852,7 +852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -864,6 +864,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -912,6 +913,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -940,9 +946,6 @@
       <c r="F2" t="n">
         <v/>
       </c>
-      <c r="G2" t="n">
-        <v/>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>completed</t>
@@ -950,7 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE — verify; 57.6% stake + mandatory open offer</t>
+          <t>VERIFIED — Proximus (via Proximus Opal) acquired 57.56% of Route Mobile at Rs 1626.40/sh for ~Rs 5922 cr; mandatory open offer 26% at same Rs 1626.40; completed May 2024; holding later reached ~82.7%; P/E unverified</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/companies/news/proximus-group-to-acquire-58-stake-in-route-mobile-for-rs-5-922-cr-123071700567_1.html</t>
         </is>
       </c>
     </row>
@@ -981,9 +989,6 @@
       <c r="F3" t="n">
         <v>1.8</v>
       </c>
-      <c r="G3" t="n">
-        <v>16</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>completed</t>
@@ -991,7 +996,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE — verify; India's first large hostile takeover; open offer at Rs 980</t>
+          <t>VERIFIED — hostile takeover; bought 20.3% from V.G. Siddhartha at Rs 980; open offer at Rs 980 (1.8% over Rs 962.5 mkt); raised stake to 51%; total ~Rs 10733 cr; EV/EBITDA and P/E unverified</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.thenewsminute.com/money/lts-hostile-takeover-bid-mindtree-explained-98608</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1626,7 @@
         <v/>
       </c>
       <c r="F2" s="14">
-        <f>B2-453.5687057188975</f>
+        <f>B2-454.35432901321394</f>
         <v/>
       </c>
     </row>
@@ -1639,7 +1649,7 @@
         <v/>
       </c>
       <c r="F3" s="14">
-        <f>B3-57.510705498698044</f>
+        <f>B3-57.11452647891894</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1672,7 @@
         <v/>
       </c>
       <c r="F4" s="14">
-        <f>B4-75.46999999999998</f>
+        <f>B4-75.5</f>
         <v/>
       </c>
     </row>
@@ -1685,7 +1695,7 @@
         <v/>
       </c>
       <c r="F5" s="14">
-        <f>B5--0.23796600637739432</f>
+        <f>B5--0.24351620557723266</f>
         <v/>
       </c>
     </row>
@@ -1832,7 +1842,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Acquiring 100% crosses the 25% threshold -&gt; mandatory open offer for 26% of the target at the floor price (modeled at the Rs 5,405 offer price; real floor is the highest-of tests incl. 60-day VWAP).</t>
+          <t>Acquiring 100% crosses the 25% threshold -&gt; mandatory open offer for 26% of the target at the floor price (modeled at the Rs 5,526 offer price; real floor is the highest-of tests incl. 60-day VWAP).</t>
         </is>
       </c>
     </row>
@@ -1846,14 +1856,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>50% acceptance: buy 2.03 Cr shares for Rs 10,978 Cr; post-offer holding 100.0%. BREACHES 75% MPS — must sell down within 12 months or pursue delisting (requires 90%).</t>
+          <t>50% acceptance: buy 2.03 Cr shares for Rs 11,222 Cr; post-offer holding 100.0%. BREACHES 75% MPS — must sell down within 12 months or pursue delisting (requires 90%).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>100% acceptance: buy 4.06 Cr shares for Rs 21,956 Cr; post-offer holding 100.0%. BREACHES 75% MPS — must sell down within 12 months or pursue delisting (requires 90%).</t>
+          <t>100% acceptance: buy 4.06 Cr shares for Rs 22,445 Cr; post-offer holding 100.0%. BREACHES 75% MPS — must sell down within 12 months or pursue delisting (requires 90%).</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1877,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deal value Rs 84,445 Cr exceeds the Rs 2,000 Cr deal-value threshold (2024 amendment) — CCI approval required; expect ~150-210 days outer timeline, Green Channel possible if no overlaps.</t>
+          <t>Deal value Rs 86,327 Cr exceeds the Rs 2,000 Cr deal-value threshold (2024 amendment) — CCI approval required; expect ~150-210 days outer timeline, Green Channel possible if no overlaps.</t>
         </is>
       </c>
     </row>
@@ -2149,31 +2159,31 @@
         <v>8</v>
       </c>
       <c r="B4" s="18" t="n">
-        <v>-16.69</v>
+        <v>-17.1</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>-16.58</v>
+        <v>-16.99</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>-16.47</v>
+        <v>-16.88</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>-16.36</v>
+        <v>-16.77</v>
       </c>
       <c r="F4" s="18" t="n">
-        <v>-16.25</v>
+        <v>-16.66</v>
       </c>
       <c r="G4" s="18" t="n">
-        <v>-16.14</v>
+        <v>-16.55</v>
       </c>
       <c r="H4" s="18" t="n">
-        <v>-16.03</v>
+        <v>-16.44</v>
       </c>
       <c r="I4" s="18" t="n">
-        <v>-15.92</v>
+        <v>-16.33</v>
       </c>
       <c r="J4" s="18" t="n">
-        <v>-15.81</v>
+        <v>-16.22</v>
       </c>
     </row>
     <row r="5">
@@ -2181,31 +2191,31 @@
         <v>10.5</v>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-17.17</v>
+        <v>-17.59</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>-17.06</v>
+        <v>-17.48</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>-16.95</v>
+        <v>-17.37</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>-16.84</v>
+        <v>-17.26</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>-16.73</v>
+        <v>-17.15</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>-16.62</v>
+        <v>-17.04</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>-16.51</v>
+        <v>-16.93</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>-16.4</v>
+        <v>-16.82</v>
       </c>
       <c r="J5" s="18" t="n">
-        <v>-16.29</v>
+        <v>-16.71</v>
       </c>
     </row>
     <row r="6">
@@ -2213,31 +2223,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>-17.65</v>
+        <v>-18.08</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>-17.54</v>
+        <v>-17.97</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>-17.43</v>
+        <v>-17.86</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>-17.32</v>
+        <v>-17.75</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>-17.21</v>
+        <v>-17.64</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>-17.1</v>
+        <v>-17.53</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>-16.99</v>
+        <v>-17.42</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>-16.88</v>
+        <v>-17.31</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>-16.77</v>
+        <v>-17.2</v>
       </c>
     </row>
     <row r="7">
@@ -2245,31 +2255,31 @@
         <v>15.5</v>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-18.13</v>
+        <v>-18.56</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>-18.02</v>
+        <v>-18.45</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>-17.91</v>
+        <v>-18.34</v>
       </c>
       <c r="E7" s="18" t="n">
+        <v>-18.23</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>-18.12</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>-18.01</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-17.9</v>
+      </c>
+      <c r="I7" s="18" t="n">
         <v>-17.8</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="J7" s="18" t="n">
         <v>-17.69</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>-17.58</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>-17.47</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>-17.36</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>-17.25</v>
       </c>
     </row>
     <row r="8">
@@ -2277,31 +2287,31 @@
         <v>18</v>
       </c>
       <c r="B8" s="18" t="n">
-        <v>-18.6</v>
+        <v>-19.04</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>-18.49</v>
+        <v>-18.93</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-18.38</v>
+        <v>-18.82</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-18.27</v>
+        <v>-18.72</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-18.16</v>
+        <v>-18.61</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-18.06</v>
+        <v>-18.5</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-17.95</v>
+        <v>-18.39</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-17.84</v>
+        <v>-18.28</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>-17.73</v>
+        <v>-18.17</v>
       </c>
     </row>
     <row r="9">
@@ -2309,31 +2319,31 @@
         <v>20.5</v>
       </c>
       <c r="B9" s="18" t="n">
-        <v>-19.07</v>
+        <v>-19.52</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>-18.97</v>
+        <v>-19.41</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>-18.86</v>
+        <v>-19.31</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-18.75</v>
+        <v>-19.2</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>-18.64</v>
+        <v>-19.09</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>-18.53</v>
+        <v>-18.98</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>-18.42</v>
+        <v>-18.87</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>-18.31</v>
+        <v>-18.76</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>-18.2</v>
+        <v>-18.65</v>
       </c>
     </row>
     <row r="10">
@@ -2341,31 +2351,31 @@
         <v>23</v>
       </c>
       <c r="B10" s="18" t="n">
-        <v>-19.55</v>
+        <v>-20</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>-19.44</v>
+        <v>-19.89</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>-19.33</v>
+        <v>-19.78</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>-19.22</v>
+        <v>-19.68</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>-19.11</v>
+        <v>-19.57</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>-19</v>
+        <v>-19.46</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>-18.89</v>
+        <v>-19.35</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>-18.78</v>
+        <v>-19.24</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>-18.68</v>
+        <v>-19.13</v>
       </c>
     </row>
     <row r="11">
@@ -2373,31 +2383,31 @@
         <v>25.5</v>
       </c>
       <c r="B11" s="18" t="n">
-        <v>-20.01</v>
+        <v>-20.48</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>-19.91</v>
+        <v>-20.37</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>-19.8</v>
+        <v>-20.26</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-19.69</v>
+        <v>-20.15</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>-19.58</v>
+        <v>-20.04</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>-19.47</v>
+        <v>-19.94</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>-19.36</v>
+        <v>-19.83</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>-19.25</v>
+        <v>-19.72</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>-19.15</v>
+        <v>-19.61</v>
       </c>
     </row>
     <row r="12">
@@ -2405,31 +2415,31 @@
         <v>28</v>
       </c>
       <c r="B12" s="18" t="n">
-        <v>-20.48</v>
+        <v>-20.95</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>-20.37</v>
+        <v>-20.84</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>-20.26</v>
+        <v>-20.73</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>-20.16</v>
+        <v>-20.63</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-20.05</v>
+        <v>-20.52</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>-19.94</v>
+        <v>-20.41</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>-19.83</v>
+        <v>-20.3</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>-19.72</v>
+        <v>-20.19</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>-19.61</v>
+        <v>-20.09</v>
       </c>
     </row>
     <row r="14">
@@ -2478,31 +2488,31 @@
         <v>0</v>
       </c>
       <c r="B16" s="18" t="n">
-        <v>-16.8</v>
+        <v>-17.17</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>-17.26</v>
+        <v>-17.64</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>-17.72</v>
+        <v>-18.1</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>-18.18</v>
+        <v>-18.56</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>-18.63</v>
+        <v>-19.02</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>-19.08</v>
+        <v>-19.48</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>-19.53</v>
+        <v>-19.93</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>-19.97</v>
+        <v>-20.38</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>-20.41</v>
+        <v>-20.82</v>
       </c>
     </row>
     <row r="17">
@@ -2510,31 +2520,31 @@
         <v>10</v>
       </c>
       <c r="B17" s="18" t="n">
-        <v>-16.67</v>
+        <v>-17.05</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>-17.14</v>
+        <v>-17.52</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>-17.6</v>
+        <v>-17.99</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>-18.06</v>
+        <v>-18.46</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>-18.52</v>
+        <v>-18.92</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>-18.98</v>
+        <v>-19.39</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>-19.43</v>
+        <v>-19.84</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>-19.88</v>
+        <v>-20.3</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>-20.33</v>
+        <v>-20.75</v>
       </c>
     </row>
     <row r="18">
@@ -2542,31 +2552,31 @@
         <v>20</v>
       </c>
       <c r="B18" s="18" t="n">
-        <v>-16.53</v>
+        <v>-16.92</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>-17.01</v>
+        <v>-17.4</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>-17.48</v>
+        <v>-17.88</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>-17.94</v>
+        <v>-18.35</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>-18.41</v>
+        <v>-18.82</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>-18.87</v>
+        <v>-19.29</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>-19.33</v>
+        <v>-19.75</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>-19.78</v>
+        <v>-20.22</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>-20.24</v>
+        <v>-20.68</v>
       </c>
     </row>
     <row r="19">
@@ -2574,31 +2584,31 @@
         <v>30</v>
       </c>
       <c r="B19" s="18" t="n">
-        <v>-16.39</v>
+        <v>-16.79</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>-16.87</v>
+        <v>-17.28</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>-17.35</v>
+        <v>-17.76</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>-17.82</v>
+        <v>-18.24</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>-18.29</v>
+        <v>-18.72</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>-18.76</v>
+        <v>-19.19</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>-19.22</v>
+        <v>-19.66</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>-19.68</v>
+        <v>-20.13</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>-20.14</v>
+        <v>-20.6</v>
       </c>
     </row>
     <row r="20">
@@ -2606,31 +2616,31 @@
         <v>40</v>
       </c>
       <c r="B20" s="18" t="n">
-        <v>-16.25</v>
+        <v>-16.66</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>-16.73</v>
+        <v>-17.15</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>-17.21</v>
+        <v>-17.64</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>-17.69</v>
+        <v>-18.12</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>-18.16</v>
+        <v>-18.61</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>-18.64</v>
+        <v>-19.09</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>-19.11</v>
+        <v>-19.57</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>-19.58</v>
+        <v>-20.04</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>-20.05</v>
+        <v>-20.52</v>
       </c>
     </row>
     <row r="21">
@@ -2638,31 +2648,31 @@
         <v>50</v>
       </c>
       <c r="B21" s="18" t="n">
-        <v>-16.1</v>
+        <v>-16.52</v>
       </c>
       <c r="C21" s="18" t="n">
-        <v>-16.59</v>
+        <v>-17.02</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>-17.07</v>
+        <v>-17.51</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>-17.56</v>
+        <v>-18</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>-18.04</v>
+        <v>-18.49</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>-18.52</v>
+        <v>-18.98</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>-19</v>
+        <v>-19.47</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>-19.47</v>
+        <v>-19.95</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>-19.95</v>
+        <v>-20.43</v>
       </c>
     </row>
     <row r="22">
@@ -2670,31 +2680,31 @@
         <v>60</v>
       </c>
       <c r="B22" s="18" t="n">
-        <v>-15.94</v>
+        <v>-16.38</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>-16.44</v>
+        <v>-16.88</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>-16.93</v>
+        <v>-17.38</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>-17.42</v>
+        <v>-17.88</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>-17.9</v>
+        <v>-18.38</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>-18.39</v>
+        <v>-18.87</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>-18.88</v>
+        <v>-19.36</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>-19.36</v>
+        <v>-19.86</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>-19.84</v>
+        <v>-20.35</v>
       </c>
     </row>
     <row r="23">
@@ -2702,31 +2712,31 @@
         <v>70</v>
       </c>
       <c r="B23" s="18" t="n">
-        <v>-15.78</v>
+        <v>-16.23</v>
       </c>
       <c r="C23" s="18" t="n">
-        <v>-16.28</v>
+        <v>-16.74</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>-16.78</v>
+        <v>-17.24</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>-17.27</v>
+        <v>-17.75</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>-17.77</v>
+        <v>-18.25</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>-18.26</v>
+        <v>-18.76</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>-18.75</v>
+        <v>-19.26</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>-19.24</v>
+        <v>-19.76</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>-19.73</v>
+        <v>-20.26</v>
       </c>
     </row>
     <row r="24">
@@ -2734,31 +2744,31 @@
         <v>80</v>
       </c>
       <c r="B24" s="18" t="n">
-        <v>-15.62</v>
+        <v>-16.08</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>-16.12</v>
+        <v>-16.59</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>-16.62</v>
+        <v>-17.1</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-17.12</v>
+        <v>-17.62</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>-17.62</v>
+        <v>-18.13</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>-18.12</v>
+        <v>-18.64</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-18.62</v>
+        <v>-19.14</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-19.12</v>
+        <v>-19.65</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>-19.62</v>
+        <v>-20.16</v>
       </c>
     </row>
     <row r="25">
@@ -2766,31 +2776,31 @@
         <v>90</v>
       </c>
       <c r="B25" s="18" t="n">
-        <v>-15.44</v>
+        <v>-15.92</v>
       </c>
       <c r="C25" s="18" t="n">
-        <v>-15.95</v>
+        <v>-16.44</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>-16.46</v>
+        <v>-16.96</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>-16.97</v>
+        <v>-17.48</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>-17.48</v>
+        <v>-17.99</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>-17.98</v>
+        <v>-18.51</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-18.49</v>
+        <v>-19.03</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>-19</v>
+        <v>-19.54</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>-19.5</v>
+        <v>-20.06</v>
       </c>
     </row>
     <row r="26">
@@ -2798,31 +2808,31 @@
         <v>100</v>
       </c>
       <c r="B26" s="18" t="n">
-        <v>-15.27</v>
+        <v>-15.75</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>-15.78</v>
+        <v>-16.28</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>-16.29</v>
+        <v>-16.81</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>-16.81</v>
+        <v>-17.33</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>-17.32</v>
+        <v>-17.86</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>-17.84</v>
+        <v>-18.38</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>-18.35</v>
+        <v>-18.91</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-18.86</v>
+        <v>-19.43</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>-19.38</v>
+        <v>-19.96</v>
       </c>
     </row>
   </sheetData>
